--- a/Test-Cases/Test-Cases-Cart.xlsx
+++ b/Test-Cases/Test-Cases-Cart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0. Documentos\Github\qa-saucedemo-testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6251A4EF-3032-4BB4-917B-941FC4BE8B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CCD4FC-C30F-4D69-B06D-886ECBBBB714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -673,7 +673,9 @@
       <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="E6" s="6" t="s">
         <v>30</v>
       </c>

--- a/Test-Cases/Test-Cases-Cart.xlsx
+++ b/Test-Cases/Test-Cases-Cart.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0. Documentos\Github\qa-saucedemo-testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CCD4FC-C30F-4D69-B06D-886ECBBBB714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D2409C-2E03-4C8A-88FC-698DB38EC8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases - Cart" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -63,12 +63,6 @@
     <t>High</t>
   </si>
   <si>
-    <t>Given the user is on the inventory page
-When they add "Sauce Labs Backpack" and "Sauce Labs Bike Light" to the cart
-Then both products appear listed when entering the cart view
-And the cart icon displays the number "2"</t>
-  </si>
-  <si>
     <t>Pass</t>
   </si>
   <si>
@@ -81,12 +75,6 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>Given the user has 2 products in the cart ("Sauce Labs Backpack" and "Sauce Labs Bike Light")
-When they enter the cart view
-And they click "Remove" on both products
-Then both products are successfully removed from the cart list</t>
-  </si>
-  <si>
     <t>TC-003</t>
   </si>
   <si>
@@ -96,33 +84,13 @@
     <t>Edge case / State Transition</t>
   </si>
   <si>
-    <t>Given the user has 4 products saved in the cart
-When they open the hamburger menu and click "Logout"
-And they log in again with the same credentials
-Then the 4 products are still present in the cart</t>
-  </si>
-  <si>
     <t>TC-004</t>
   </si>
   <si>
     <t>Return to inventory from the cart without losing the session</t>
   </si>
   <si>
-    <t>Both products were added successfully and appear correctly listed in the cart.</t>
-  </si>
-  <si>
     <t>Both products were removed successfully from the cart.</t>
-  </si>
-  <si>
-    <t>As expected, though possibly by design rather than a bug: cart is not cleared on logout, products persist across the logout/login transition.</t>
-  </si>
-  <si>
-    <t>Given the user has products saved in the cart
-When they return to the inventory page using the "Continue Shopping" button, or using the browser's back arrow
-Then the session remains active and the user stays logged in, with the cart items unaffected</t>
-  </si>
-  <si>
-    <t>As expected: the session remains active after returning to the inventory from the cart, using either the "Continue Shopping" button or the browser's back arrow.</t>
   </si>
   <si>
     <t>TC-005</t>
@@ -137,13 +105,46 @@
     <t>Fail</t>
   </si>
   <si>
-    <t>The system does not block or warn. It allows the user to proceed directly to the checkout form with 0 items in the cart.</t>
-  </si>
-  <si>
-    <t>Checkout is allowed with an empty cart</t>
-  </si>
-  <si>
     <t>Negative / Edge case</t>
+  </si>
+  <si>
+    <t>Given the user has 2 products in the cart ("Sauce Labs Backpack" and "Sauce Labs Bike Light")
+When they enter the cart view
+And they click "Remove" on both products
+Then both products should be successfully removed from the cart list</t>
+  </si>
+  <si>
+    <t>Given the user has 4 products saved in the cart
+When they open the hamburger menu and click "Logout"
+And they log in again with the same valid credentials
+Then the 4 products should still be present in the cart, since the user's selection is expected to be preserved between sessions</t>
+  </si>
+  <si>
+    <t>The 4 products are still present in the cart after logging back in.</t>
+  </si>
+  <si>
+    <t>Given the user is logged in with products saved in the cart
+And the user is on the cart page
+When they return to the inventory page using each of these options, one at a time: the "Continue Shopping" button and the browser's back arrow
+Then in both cases the session should remain active, the user should stay logged in, and the cart items should be unaffected</t>
+  </si>
+  <si>
+    <t>The session remains active and the cart items are unaffected when returning with the "Continue Shopping" button and with the browser's back arrow.</t>
+  </si>
+  <si>
+    <t>Given the user is on the inventory page
+When they add "Sauce Labs Backpack" and "Sauce Labs Bike Light" to the cart
+Then both products should be listed in the cart view
+And the cart icon should display the number "2"</t>
+  </si>
+  <si>
+    <t>Both products are listed in the cart and the cart icon displays "2".</t>
+  </si>
+  <si>
+    <t>Proceed to checkout with an empty cart</t>
+  </si>
+  <si>
+    <t>Then the system should not allow proceeding to checkout, and should indicate that the cart is empty</t>
   </si>
 </sst>
 </file>
@@ -241,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -261,9 +262,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,7 +543,7 @@
     <col min="5" max="5" width="75" customWidth="1"/>
     <col min="6" max="6" width="55" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -563,7 +568,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -581,116 +586,126 @@
         <v>11</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="7">
+        <v>46308</v>
+      </c>
     </row>
     <row r="3" spans="1:8" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="H3" s="7">
+        <v>46308</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="7">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="H5" s="7">
+        <v>46308</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="7">
+        <v>46308</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G5" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G6" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Pass,Fail,Blocked,Pending"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/Test-Cases/Test-Cases-Cart.xlsx
+++ b/Test-Cases/Test-Cases-Cart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0. Documentos\Github\qa-saucedemo-testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D2409C-2E03-4C8A-88FC-698DB38EC8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A041803-7192-4299-A0FB-52E3C9FE09F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,28 +96,10 @@
     <t>TC-005</t>
   </si>
   <si>
-    <t>Given the user is logged in with an empty cart (no products added)
-When they navigate to the cart view
-And they click "Checkout"
-Then the system should ideally block the action or display a warning indicating the cart is empty</t>
-  </si>
-  <si>
     <t>Fail</t>
   </si>
   <si>
     <t>Negative / Edge case</t>
-  </si>
-  <si>
-    <t>Given the user has 2 products in the cart ("Sauce Labs Backpack" and "Sauce Labs Bike Light")
-When they enter the cart view
-And they click "Remove" on both products
-Then both products should be successfully removed from the cart list</t>
-  </si>
-  <si>
-    <t>Given the user has 4 products saved in the cart
-When they open the hamburger menu and click "Logout"
-And they log in again with the same valid credentials
-Then the 4 products should still be present in the cart, since the user's selection is expected to be preserved between sessions</t>
   </si>
   <si>
     <t>The 4 products are still present in the cart after logging back in.</t>
@@ -132,19 +114,39 @@
     <t>The session remains active and the cart items are unaffected when returning with the "Continue Shopping" button and with the browser's back arrow.</t>
   </si>
   <si>
-    <t>Given the user is on the inventory page
+    <t>Both products are listed in the cart and the cart icon displays "2".</t>
+  </si>
+  <si>
+    <t>Proceed to checkout with an empty cart</t>
+  </si>
+  <si>
+    <t>The system allows proceeding to the checkout form with an empty cart and shows no message about the empty cart.</t>
+  </si>
+  <si>
+    <t>Given the user is logged in with an empty cart
+And the user is on the inventory page
 When they add "Sauce Labs Backpack" and "Sauce Labs Bike Light" to the cart
 Then both products should be listed in the cart view
 And the cart icon should display the number "2"</t>
   </si>
   <si>
-    <t>Both products are listed in the cart and the cart icon displays "2".</t>
-  </si>
-  <si>
-    <t>Proceed to checkout with an empty cart</t>
-  </si>
-  <si>
-    <t>Then the system should not allow proceeding to checkout, and should indicate that the cart is empty</t>
+    <t>Given the user is logged in with an empty cart
+And the user is on the inventory page
+When they navigate to the cart view
+And they click "Checkout"
+Then the system should not allow proceeding to checkout, and should indicate that the cart is empty</t>
+  </si>
+  <si>
+    <t>Given the user is logged in with 2 products in the cart ("Sauce Labs Backpack" and "Sauce Labs Bike Light")
+When they enter the cart view
+And they click "Remove" on both products
+Then both products should be successfully removed from the cart list</t>
+  </si>
+  <si>
+    <t>Given the user is logged in with 4 different products in the cart
+When they open the hamburger menu and click "Logout"
+And they log in again with the same valid credentials
+Then the same 4 products should still be present in the cart, since the user's selection is expected to be preserved between sessions</t>
   </si>
 </sst>
 </file>
@@ -572,7 +574,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -589,7 +591,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
@@ -612,7 +614,7 @@
         <v>15</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>21</v>
@@ -638,10 +640,10 @@
         <v>15</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>12</v>
@@ -664,10 +666,10 @@
         <v>15</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>12</v>
@@ -676,27 +678,27 @@
         <v>46308</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="84.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="H6" s="7">
         <v>46308</v>
